--- a/Scripts_Data/CFL_Results.xlsx
+++ b/Scripts_Data/CFL_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\simscape\demo\multibody\contact-forces-library\Scripts_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A45E042-1334-433B-AC32-0CED2A278998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844FE297-36DF-4083-A57B-547C62D6C93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="1665" windowWidth="26370" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -225,10 +225,7 @@
     <t>CFL v5.0</t>
   </si>
   <si>
-    <t>25.2.0.3042426 (R2025b) Update 1</t>
-  </si>
-  <si>
-    <t>17-Dec-2025 18:38:30</t>
+    <t>26.1.0.3203278 (R2026a)</t>
   </si>
 </sst>
 </file>
@@ -723,8 +720,8 @@
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="19" t="s">
-        <v>66</v>
+      <c r="F1" s="19">
+        <v>46132.813321759262</v>
       </c>
       <c r="G1" s="19"/>
       <c r="H1" s="14" t="s">
@@ -798,25 +795,25 @@
         <v>2872</v>
       </c>
       <c r="E4" s="15">
-        <v>0.45100000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="F4" s="15">
         <v>2872</v>
       </c>
       <c r="G4" s="15">
-        <v>0.17299999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="H4" s="15">
         <v>2872</v>
       </c>
       <c r="I4" s="15">
-        <v>0.16400000000000001</v>
+        <v>0.152</v>
       </c>
       <c r="J4" s="15">
         <v>2872</v>
       </c>
       <c r="K4" s="15">
-        <v>0.14399999999999999</v>
+        <v>0.13900000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -833,25 +830,25 @@
         <v>743</v>
       </c>
       <c r="E5" s="3">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F5" s="3">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G5" s="3">
-        <v>0.09</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="H5" s="3">
         <v>781</v>
       </c>
       <c r="I5" s="3">
-        <v>5.6000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J5" s="3">
         <v>1045</v>
       </c>
       <c r="K5" s="3">
-        <v>5.6000000000000001E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -868,25 +865,25 @@
         <v>491</v>
       </c>
       <c r="E6" s="3">
-        <v>0.11700000000000001</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F6" s="3">
         <v>526</v>
       </c>
       <c r="G6" s="3">
-        <v>4.4999999999999998E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="H6" s="3">
         <v>513</v>
       </c>
       <c r="I6" s="3">
-        <v>4.4999999999999998E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J6" s="3">
         <v>553</v>
       </c>
       <c r="K6" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -903,25 +900,25 @@
         <v>4218</v>
       </c>
       <c r="E7" s="3">
-        <v>2.3860000000000001</v>
+        <v>1.411</v>
       </c>
       <c r="F7" s="3">
         <v>4776</v>
       </c>
       <c r="G7" s="3">
-        <v>1.3029999999999999</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="H7" s="3">
         <v>5370</v>
       </c>
       <c r="I7" s="3">
-        <v>1.5329999999999999</v>
+        <v>1.556</v>
       </c>
       <c r="J7" s="3">
         <v>6259</v>
       </c>
       <c r="K7" s="3">
-        <v>2.0019999999999998</v>
+        <v>2.0670000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -935,28 +932,28 @@
         <v>5</v>
       </c>
       <c r="D8" s="3">
-        <v>2347</v>
+        <v>2356</v>
       </c>
       <c r="E8" s="3">
-        <v>0.193</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F8" s="3">
-        <v>2825</v>
+        <v>2828</v>
       </c>
       <c r="G8" s="3">
-        <v>0.159</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="H8" s="3">
         <v>2579</v>
       </c>
       <c r="I8" s="3">
-        <v>0.14899999999999999</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="J8" s="3">
-        <v>3090</v>
+        <v>3077</v>
       </c>
       <c r="K8" s="3">
-        <v>0.152</v>
+        <v>0.16200000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -973,25 +970,25 @@
         <v>775</v>
       </c>
       <c r="E9" s="3">
-        <v>0.16900000000000001</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="F9" s="3">
         <v>528</v>
       </c>
       <c r="G9" s="3">
-        <v>7.6999999999999999E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="H9" s="3">
         <v>854</v>
       </c>
       <c r="I9" s="3">
-        <v>0.109</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J9" s="3">
         <v>541</v>
       </c>
       <c r="K9" s="3">
-        <v>7.5999999999999998E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1008,19 +1005,19 @@
         <v>220</v>
       </c>
       <c r="E10" s="3">
-        <v>8.5000000000000006E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F10" s="3">
         <v>225</v>
       </c>
       <c r="G10" s="3">
-        <v>2.5999999999999999E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="H10" s="3">
         <v>235</v>
       </c>
       <c r="I10" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="J10" s="3">
         <v>235</v>
@@ -1043,25 +1040,25 @@
         <v>24447</v>
       </c>
       <c r="E11" s="3">
-        <v>3.476</v>
+        <v>2.9239999999999999</v>
       </c>
       <c r="F11" s="3">
         <v>51846</v>
       </c>
       <c r="G11" s="3">
-        <v>5.9009999999999998</v>
+        <v>5.6589999999999998</v>
       </c>
       <c r="H11" s="3">
         <v>26130</v>
       </c>
       <c r="I11" s="3">
-        <v>3.13</v>
+        <v>4.1859999999999999</v>
       </c>
       <c r="J11" s="3">
         <v>55776</v>
       </c>
       <c r="K11" s="3">
-        <v>6.8029999999999999</v>
+        <v>12.129</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1078,25 +1075,25 @@
         <v>1137</v>
       </c>
       <c r="E12" s="3">
-        <v>0.11</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="F12" s="3">
         <v>1137</v>
       </c>
       <c r="G12" s="3">
-        <v>4.9000000000000002E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="H12" s="3">
         <v>1137</v>
       </c>
       <c r="I12" s="3">
-        <v>5.3999999999999999E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J12" s="3">
         <v>1137</v>
       </c>
       <c r="K12" s="3">
-        <v>0.05</v>
+        <v>6.0999999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1119,19 +1116,19 @@
         <v>1401</v>
       </c>
       <c r="G13" s="3">
-        <v>0.11899999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="H13" s="3">
         <v>1398</v>
       </c>
       <c r="I13" s="3">
-        <v>0.105</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J13" s="3">
         <v>1490</v>
       </c>
       <c r="K13" s="3">
-        <v>0.125</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1145,28 +1142,28 @@
         <v>45</v>
       </c>
       <c r="D14" s="3">
-        <v>5512</v>
+        <v>5550</v>
       </c>
       <c r="E14" s="3">
-        <v>0.23599999999999999</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="F14" s="3">
-        <v>5512</v>
+        <v>5550</v>
       </c>
       <c r="G14" s="3">
-        <v>0.187</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="H14" s="3">
-        <v>5512</v>
+        <v>5550</v>
       </c>
       <c r="I14" s="3">
-        <v>0.14000000000000001</v>
+        <v>0.253</v>
       </c>
       <c r="J14" s="3">
-        <v>5512</v>
+        <v>5550</v>
       </c>
       <c r="K14" s="3">
-        <v>0.13900000000000001</v>
+        <v>0.28299999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1183,25 +1180,25 @@
         <v>821</v>
       </c>
       <c r="E15" s="3">
-        <v>0.14099999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="F15" s="3">
         <v>938</v>
       </c>
       <c r="G15" s="3">
-        <v>5.6000000000000001E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="H15" s="3">
         <v>864</v>
       </c>
       <c r="I15" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="J15" s="3">
-        <v>1012</v>
+        <v>980</v>
       </c>
       <c r="K15" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1218,25 +1215,25 @@
         <v>1450</v>
       </c>
       <c r="E16" s="3">
-        <v>0.13300000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="F16" s="3">
         <v>1516</v>
       </c>
       <c r="G16" s="3">
-        <v>7.5999999999999998E-2</v>
+        <v>0.109</v>
       </c>
       <c r="H16" s="3">
         <v>1501</v>
       </c>
       <c r="I16" s="3">
-        <v>6.7000000000000004E-2</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="J16" s="3">
         <v>1562</v>
       </c>
       <c r="K16" s="3">
-        <v>7.9000000000000001E-2</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1253,25 +1250,25 @@
         <v>5901</v>
       </c>
       <c r="E17" s="3">
-        <v>1.8540000000000001</v>
+        <v>1.284</v>
       </c>
       <c r="F17" s="3">
         <v>6071</v>
       </c>
       <c r="G17" s="3">
-        <v>0.80800000000000005</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="H17" s="3">
         <v>6216</v>
       </c>
       <c r="I17" s="3">
-        <v>0.55400000000000005</v>
+        <v>0.82</v>
       </c>
       <c r="J17" s="3">
         <v>6507</v>
       </c>
       <c r="K17" s="3">
-        <v>0.63700000000000001</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1288,25 +1285,25 @@
         <v>293</v>
       </c>
       <c r="E18" s="3">
-        <v>8.6999999999999994E-2</v>
+        <v>0.109</v>
       </c>
       <c r="F18" s="3">
         <v>323</v>
       </c>
       <c r="G18" s="3">
-        <v>4.4999999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="H18" s="3">
         <v>317</v>
       </c>
       <c r="I18" s="3">
-        <v>4.5999999999999999E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="J18" s="3">
         <v>345</v>
       </c>
       <c r="K18" s="3">
-        <v>5.2999999999999999E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1323,25 +1320,25 @@
         <v>3564</v>
       </c>
       <c r="E19" s="3">
-        <v>0.76300000000000001</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="F19" s="3">
         <v>3636</v>
       </c>
       <c r="G19" s="3">
-        <v>0.373</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="H19" s="3">
         <v>3609</v>
       </c>
       <c r="I19" s="3">
-        <v>0.224</v>
+        <v>0.437</v>
       </c>
       <c r="J19" s="3">
         <v>3751</v>
       </c>
       <c r="K19" s="3">
-        <v>0.25700000000000001</v>
+        <v>0.58699999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,25 +1355,25 @@
         <v>6943</v>
       </c>
       <c r="E20" s="3">
-        <v>0.80700000000000005</v>
+        <v>1.1180000000000001</v>
       </c>
       <c r="F20" s="3">
         <v>7054</v>
       </c>
       <c r="G20" s="3">
-        <v>0.505</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="H20" s="3">
         <v>164459</v>
       </c>
       <c r="I20" s="3">
-        <v>8.4640000000000004</v>
+        <v>11.882999999999999</v>
       </c>
       <c r="J20" s="3">
         <v>175049</v>
       </c>
       <c r="K20" s="3">
-        <v>9.1059999999999999</v>
+        <v>12.53</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,25 +1390,25 @@
         <v>3444</v>
       </c>
       <c r="E21" s="3">
-        <v>0.19500000000000001</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="F21" s="3">
         <v>3602</v>
       </c>
       <c r="G21" s="3">
-        <v>0.20599999999999999</v>
+        <v>0.248</v>
       </c>
       <c r="H21" s="3">
         <v>3940</v>
       </c>
       <c r="I21" s="3">
-        <v>0.192</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="J21" s="3">
         <v>4310</v>
       </c>
       <c r="K21" s="3">
-        <v>0.20599999999999999</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1425,28 +1422,28 @@
         <v>10</v>
       </c>
       <c r="D22" s="3">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="E22" s="8">
-        <v>2.7480000000000002</v>
+        <v>3.2330000000000001</v>
       </c>
       <c r="F22" s="3">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="G22" s="3">
-        <v>1.968</v>
+        <v>3.008</v>
       </c>
       <c r="H22" s="3">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="I22" s="3">
-        <v>2.0390000000000001</v>
+        <v>2.6440000000000001</v>
       </c>
       <c r="J22" s="3">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="K22" s="3">
-        <v>2.1619999999999999</v>
+        <v>2.5950000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1463,25 +1460,25 @@
         <v>2720</v>
       </c>
       <c r="E23" s="8">
-        <v>1.1879999999999999</v>
+        <v>1.827</v>
       </c>
       <c r="F23" s="3">
         <v>2783</v>
       </c>
       <c r="G23" s="3">
-        <v>0.63100000000000001</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="H23" s="3">
         <v>3463</v>
       </c>
       <c r="I23" s="3">
-        <v>0.64100000000000001</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J23" s="3">
         <v>3610</v>
       </c>
       <c r="K23" s="3">
-        <v>0.80100000000000005</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1498,25 +1495,25 @@
         <v>147</v>
       </c>
       <c r="E24" s="8">
-        <v>7.8E-2</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F24" s="3">
         <v>147</v>
       </c>
       <c r="G24" s="3">
-        <v>2.8000000000000001E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="H24" s="3">
         <v>147</v>
       </c>
       <c r="I24" s="3">
-        <v>3.1E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="J24" s="3">
         <v>147</v>
       </c>
       <c r="K24" s="3">
-        <v>2.9000000000000001E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1533,25 +1530,25 @@
         <v>4818</v>
       </c>
       <c r="E25" s="8">
-        <v>3.0070000000000001</v>
+        <v>3.0979999999999999</v>
       </c>
       <c r="F25" s="3">
-        <v>5231</v>
+        <v>5227</v>
       </c>
       <c r="G25" s="3">
-        <v>2.794</v>
+        <v>3.0720000000000001</v>
       </c>
       <c r="H25" s="3">
         <v>4835</v>
       </c>
       <c r="I25" s="3">
-        <v>2.4449999999999998</v>
+        <v>2.8540000000000001</v>
       </c>
       <c r="J25" s="3">
-        <v>5297</v>
+        <v>5305</v>
       </c>
       <c r="K25" s="3">
-        <v>2.54</v>
+        <v>3.1549999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1565,28 +1562,28 @@
         <v>12</v>
       </c>
       <c r="D26" s="3">
-        <v>13465</v>
+        <v>13445</v>
       </c>
       <c r="E26" s="8">
-        <v>2.7890000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="F26" s="3">
-        <v>13641</v>
+        <v>13741</v>
       </c>
       <c r="G26" s="3">
-        <v>2.7770000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="H26" s="3">
-        <v>19549</v>
+        <v>17921</v>
       </c>
       <c r="I26" s="3">
-        <v>3.62</v>
+        <v>4.3550000000000004</v>
       </c>
       <c r="J26" s="3">
-        <v>17458</v>
+        <v>18604</v>
       </c>
       <c r="K26" s="3">
-        <v>4.8010000000000002</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1603,25 +1600,25 @@
         <v>3402</v>
       </c>
       <c r="E27" s="8">
-        <v>2.036</v>
+        <v>1.7709999999999999</v>
       </c>
       <c r="F27" s="3">
         <v>3938</v>
       </c>
       <c r="G27" s="3">
-        <v>1.8340000000000001</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="H27" s="3">
         <v>3538</v>
       </c>
       <c r="I27" s="3">
-        <v>1.466</v>
+        <v>1.4430000000000001</v>
       </c>
       <c r="J27" s="3">
         <v>4199</v>
       </c>
       <c r="K27" s="3">
-        <v>2.073</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1638,25 +1635,25 @@
         <v>941</v>
       </c>
       <c r="E28" s="8">
-        <v>0.26700000000000002</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="F28" s="3">
         <v>1018</v>
       </c>
       <c r="G28" s="3">
-        <v>0.128</v>
+        <v>0.108</v>
       </c>
       <c r="H28" s="3">
         <v>967</v>
       </c>
       <c r="I28" s="3">
-        <v>0.108</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J28" s="3">
         <v>1070</v>
       </c>
       <c r="K28" s="3">
-        <v>0.13300000000000001</v>
+        <v>9.7000000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1673,25 +1670,25 @@
         <v>757</v>
       </c>
       <c r="E29" s="8">
-        <v>0.17399999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="F29" s="3">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G29" s="3">
-        <v>0.14699999999999999</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="H29" s="3">
         <v>792</v>
       </c>
       <c r="I29" s="3">
-        <v>0.13</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="J29" s="3">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="K29" s="3">
-        <v>0.16700000000000001</v>
+        <v>0.11899999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1708,25 +1705,25 @@
         <v>10374</v>
       </c>
       <c r="E30" s="8">
-        <v>24.03</v>
+        <v>7.6449999999999996</v>
       </c>
       <c r="F30" s="3">
-        <v>12217</v>
+        <v>12258</v>
       </c>
       <c r="G30" s="3">
-        <v>48.481999999999999</v>
+        <v>13.021000000000001</v>
       </c>
       <c r="H30" s="3">
         <v>11929</v>
       </c>
       <c r="I30" s="3">
-        <v>33.524000000000001</v>
+        <v>11.035</v>
       </c>
       <c r="J30" s="3">
-        <v>13505</v>
+        <v>13366</v>
       </c>
       <c r="K30" s="3">
-        <v>18.594999999999999</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1743,25 +1740,25 @@
         <v>878</v>
       </c>
       <c r="E31" s="8">
-        <v>0.24099999999999999</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="F31" s="3">
         <v>917</v>
       </c>
       <c r="G31" s="3">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="H31" s="3">
         <v>868</v>
       </c>
       <c r="I31" s="3">
-        <v>0.158</v>
+        <v>0.19</v>
       </c>
       <c r="J31" s="3">
         <v>950</v>
       </c>
       <c r="K31" s="3">
-        <v>0.14899999999999999</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1778,25 +1775,25 @@
         <v>2434</v>
       </c>
       <c r="E32" s="8">
-        <v>1.7430000000000001</v>
+        <v>1.4510000000000001</v>
       </c>
       <c r="F32" s="3">
         <v>5466</v>
       </c>
       <c r="G32" s="3">
-        <v>5.5490000000000004</v>
+        <v>5.069</v>
       </c>
       <c r="H32" s="3">
         <v>2513</v>
       </c>
       <c r="I32" s="3">
-        <v>1.151</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="J32" s="3">
         <v>6265</v>
       </c>
       <c r="K32" s="3">
-        <v>6.9039999999999999</v>
+        <v>5.915</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1813,25 +1810,25 @@
         <v>2684</v>
       </c>
       <c r="E33" s="8">
-        <v>0.74</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="F33" s="3">
         <v>4063</v>
       </c>
       <c r="G33" s="3">
-        <v>0.77700000000000002</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="H33" s="3">
         <v>3055</v>
       </c>
       <c r="I33" s="3">
-        <v>0.34799999999999998</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="J33" s="3">
         <v>4462</v>
       </c>
       <c r="K33" s="3">
-        <v>0.66700000000000004</v>
+        <v>0.70699999999999996</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1848,25 +1845,25 @@
         <v>472</v>
       </c>
       <c r="E34" s="8">
-        <v>0.19</v>
+        <v>0.755</v>
       </c>
       <c r="F34" s="3">
         <v>887</v>
       </c>
       <c r="G34" s="3">
-        <v>0.77400000000000002</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H34" s="3">
         <v>511</v>
       </c>
       <c r="I34" s="3">
-        <v>0.107</v>
+        <v>0.112</v>
       </c>
       <c r="J34" s="3">
         <v>856</v>
       </c>
       <c r="K34" s="3">
-        <v>0.42799999999999999</v>
+        <v>0.41299999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1883,25 +1880,25 @@
         <v>1735</v>
       </c>
       <c r="E35" s="8">
-        <v>0.73</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F35" s="3">
         <v>3261</v>
       </c>
       <c r="G35" s="3">
-        <v>0.96399999999999997</v>
+        <v>1.375</v>
       </c>
       <c r="H35" s="3">
         <v>1748</v>
       </c>
       <c r="I35" s="3">
-        <v>0.192</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="J35" s="3">
         <v>3277</v>
       </c>
       <c r="K35" s="3">
-        <v>0.93700000000000006</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1918,25 +1915,25 @@
         <v>10291</v>
       </c>
       <c r="E36" s="8">
-        <v>2.1749999999999998</v>
+        <v>2.1859999999999999</v>
       </c>
       <c r="F36" s="3">
-        <v>16038</v>
+        <v>16024</v>
       </c>
       <c r="G36" s="3">
-        <v>3.43</v>
+        <v>3.3410000000000002</v>
       </c>
       <c r="H36" s="3">
         <v>10364</v>
       </c>
       <c r="I36" s="3">
-        <v>2.0430000000000001</v>
+        <v>1.4570000000000001</v>
       </c>
       <c r="J36" s="3">
-        <v>16313</v>
+        <v>16354</v>
       </c>
       <c r="K36" s="3">
-        <v>3.5059999999999998</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -1953,25 +1950,25 @@
         <v>6519</v>
       </c>
       <c r="E37" s="8">
-        <v>1.077</v>
+        <v>1.089</v>
       </c>
       <c r="F37" s="3">
-        <v>10965</v>
+        <v>10972</v>
       </c>
       <c r="G37" s="3">
-        <v>1.8580000000000001</v>
+        <v>1.8480000000000001</v>
       </c>
       <c r="H37" s="3">
         <v>6644</v>
       </c>
       <c r="I37" s="3">
-        <v>0.53100000000000003</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="J37" s="3">
-        <v>10952</v>
+        <v>10995</v>
       </c>
       <c r="K37" s="3">
-        <v>1.7</v>
+        <v>1.873</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1988,25 +1985,25 @@
         <v>4176</v>
       </c>
       <c r="E38" s="8">
-        <v>1.3009999999999999</v>
+        <v>1.282</v>
       </c>
       <c r="F38" s="3">
-        <v>4663</v>
+        <v>4686</v>
       </c>
       <c r="G38" s="3">
-        <v>1.079</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="H38" s="3">
         <v>4245</v>
       </c>
       <c r="I38" s="3">
-        <v>0.81699999999999995</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="J38" s="3">
-        <v>4707</v>
+        <v>4750</v>
       </c>
       <c r="K38" s="3">
-        <v>1.002</v>
+        <v>1.1180000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2023,25 +2020,25 @@
         <v>2520</v>
       </c>
       <c r="E39" s="8">
-        <v>0.32300000000000001</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="F39" s="3">
         <v>3058</v>
       </c>
       <c r="G39" s="3">
-        <v>0.66100000000000003</v>
+        <v>0.317</v>
       </c>
       <c r="H39" s="3">
         <v>2633</v>
       </c>
       <c r="I39" s="3">
-        <v>0.247</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="J39" s="3">
         <v>3070</v>
       </c>
       <c r="K39" s="3">
-        <v>0.504</v>
+        <v>0.60599999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2058,25 +2055,25 @@
         <v>4113</v>
       </c>
       <c r="E40" s="8">
-        <v>1.577</v>
+        <v>1.569</v>
       </c>
       <c r="F40" s="3">
         <v>4559</v>
       </c>
       <c r="G40" s="3">
-        <v>1.377</v>
+        <v>1.44</v>
       </c>
       <c r="H40" s="3">
         <v>4237</v>
       </c>
       <c r="I40" s="3">
-        <v>1.4319999999999999</v>
+        <v>1.276</v>
       </c>
       <c r="J40" s="3">
-        <v>4617</v>
+        <v>4624</v>
       </c>
       <c r="K40" s="3">
-        <v>1.702</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2093,25 +2090,25 @@
         <v>4597</v>
       </c>
       <c r="E41" s="8">
-        <v>1.488</v>
+        <v>1.3280000000000001</v>
       </c>
       <c r="F41" s="3">
-        <v>4472</v>
+        <v>4566</v>
       </c>
       <c r="G41" s="3">
-        <v>1.048</v>
+        <v>1.0469999999999999</v>
       </c>
       <c r="H41" s="3">
         <v>4746</v>
       </c>
       <c r="I41" s="3">
-        <v>1.0489999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="J41" s="3">
-        <v>4629</v>
+        <v>4613</v>
       </c>
       <c r="K41" s="3">
-        <v>1.1479999999999999</v>
+        <v>1.038</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -2128,25 +2125,25 @@
         <v>6021</v>
       </c>
       <c r="E42" s="8">
-        <v>0.85799999999999998</v>
+        <v>1.2569999999999999</v>
       </c>
       <c r="F42" s="3">
         <v>6493</v>
       </c>
       <c r="G42" s="3">
-        <v>0.86899999999999999</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="H42" s="3">
         <v>6384</v>
       </c>
       <c r="I42" s="3">
-        <v>0.51500000000000001</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="J42" s="3">
         <v>6783</v>
       </c>
       <c r="K42" s="3">
-        <v>0.66200000000000003</v>
+        <v>0.76700000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2163,25 +2160,25 @@
         <v>1396</v>
       </c>
       <c r="E43" s="8">
-        <v>0.27500000000000002</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="F43" s="3">
         <v>1498</v>
       </c>
       <c r="G43" s="3">
-        <v>0.67100000000000004</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H43" s="3">
         <v>1417</v>
       </c>
       <c r="I43" s="3">
-        <v>0.26</v>
+        <v>0.223</v>
       </c>
       <c r="J43" s="3">
         <v>1473</v>
       </c>
       <c r="K43" s="3">
-        <v>0.51800000000000002</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2195,28 +2192,28 @@
         <v>24</v>
       </c>
       <c r="D44" s="3">
-        <v>7678</v>
+        <v>7582</v>
       </c>
       <c r="E44" s="8">
-        <v>2.4550000000000001</v>
+        <v>2.4060000000000001</v>
       </c>
       <c r="F44" s="3">
-        <v>7053</v>
+        <v>6881</v>
       </c>
       <c r="G44" s="3">
-        <v>3.11</v>
+        <v>3.032</v>
       </c>
       <c r="H44" s="3">
         <v>8314</v>
       </c>
       <c r="I44" s="3">
-        <v>2.1429999999999998</v>
+        <v>2.0009999999999999</v>
       </c>
       <c r="J44" s="3">
-        <v>7127</v>
+        <v>7104</v>
       </c>
       <c r="K44" s="3">
-        <v>4.4690000000000003</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2230,28 +2227,28 @@
         <v>30</v>
       </c>
       <c r="D45" s="3">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="E45" s="8">
-        <v>1.4910000000000001</v>
+        <v>1.448</v>
       </c>
       <c r="F45" s="3">
-        <v>4265</v>
+        <v>4162</v>
       </c>
       <c r="G45" s="3">
-        <v>1.056</v>
+        <v>1.073</v>
       </c>
       <c r="H45" s="3">
         <v>4041</v>
       </c>
       <c r="I45" s="3">
-        <v>1.0580000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="J45" s="3">
-        <v>4256</v>
+        <v>4185</v>
       </c>
       <c r="K45" s="3">
-        <v>1.095</v>
+        <v>1.1579999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2265,28 +2262,28 @@
         <v>30</v>
       </c>
       <c r="D46" s="3">
-        <v>4720</v>
+        <v>4854</v>
       </c>
       <c r="E46" s="8">
-        <v>2.5270000000000001</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="F46" s="3">
-        <v>4720</v>
+        <v>4854</v>
       </c>
       <c r="G46" s="3">
-        <v>2.3039999999999998</v>
+        <v>2.3239999999999998</v>
       </c>
       <c r="H46" s="3">
-        <v>4720</v>
+        <v>4854</v>
       </c>
       <c r="I46" s="3">
-        <v>2.1389999999999998</v>
+        <v>2.2709999999999999</v>
       </c>
       <c r="J46" s="3">
-        <v>4720</v>
+        <v>4854</v>
       </c>
       <c r="K46" s="3">
-        <v>2.367</v>
+        <v>2.3860000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2303,25 +2300,25 @@
         <v>6109</v>
       </c>
       <c r="E47" s="8">
-        <v>3.4350000000000001</v>
+        <v>3.2970000000000002</v>
       </c>
       <c r="F47" s="3">
-        <v>9152</v>
+        <v>9169</v>
       </c>
       <c r="G47" s="3">
-        <v>5.452</v>
+        <v>5.0709999999999997</v>
       </c>
       <c r="H47" s="3">
         <v>6004</v>
       </c>
       <c r="I47" s="3">
-        <v>3.0489999999999999</v>
+        <v>2.7269999999999999</v>
       </c>
       <c r="J47" s="3">
-        <v>9349</v>
+        <v>9357</v>
       </c>
       <c r="K47" s="3">
-        <v>6.6769999999999996</v>
+        <v>5.1749999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2338,7 +2335,7 @@
         <v>4718</v>
       </c>
       <c r="E48" s="8">
-        <v>2.4889999999999999</v>
+        <v>2.5649999999999999</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>11</v>
@@ -2373,7 +2370,7 @@
         <v>4610</v>
       </c>
       <c r="E49" s="8">
-        <v>2.4660000000000002</v>
+        <v>2.4460000000000002</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>11</v>
@@ -2408,7 +2405,7 @@
         <v>7916</v>
       </c>
       <c r="E50" s="8">
-        <v>3.4790000000000001</v>
+        <v>3.9079999999999999</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>11</v>
@@ -2443,7 +2440,7 @@
         <v>5541</v>
       </c>
       <c r="E51" s="8">
-        <v>2.823</v>
+        <v>3.1779999999999999</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>11</v>
@@ -2478,7 +2475,7 @@
         <v>4821</v>
       </c>
       <c r="E52" s="8">
-        <v>1.9259999999999999</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>11</v>
@@ -2513,7 +2510,7 @@
         <v>5858</v>
       </c>
       <c r="E53" s="8">
-        <v>3.859</v>
+        <v>4.3890000000000002</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>11</v>
@@ -2548,7 +2545,7 @@
         <v>6036</v>
       </c>
       <c r="E54" s="8">
-        <v>3.141</v>
+        <v>3.7370000000000001</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>11</v>
@@ -2583,7 +2580,7 @@
         <v>6345</v>
       </c>
       <c r="E55" s="8">
-        <v>4.5090000000000003</v>
+        <v>5.7119999999999997</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>11</v>
@@ -2618,7 +2615,7 @@
         <v>5172</v>
       </c>
       <c r="E56" s="8">
-        <v>3.6760000000000002</v>
+        <v>4.33</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>11</v>
@@ -2653,15 +2650,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -2707,18 +2695,16 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e7c50fe4-4c86-4d33-a0d3-ad29cfb7378a" ContentTypeId="0x0101" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100525B94EEF47D42499A62120CC90E0AB3" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e706cd362d7e41030bb8c72a7c62a9d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5c85acdc-a394-4ae0-8c72-fb4a95b3d573" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="55e2521e7df4d5c11309cefaa7c01562" ns2:_="">
     <xsd:import namespace="5c85acdc-a394-4ae0-8c72-fb4a95b3d573"/>
@@ -2863,7 +2849,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="e7c50fe4-4c86-4d33-a0d3-ad29cfb7378a" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE6D0D52-57FE-48CB-8E43-11384E6CFEE8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B630E037-F79E-4175-B540-A23B306F8900}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2871,18 +2876,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE6D0D52-57FE-48CB-8E43-11384E6CFEE8}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97465A2D-9EAF-44EA-B51B-9ABE6C271840}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{039CDCF7-1F8F-4E25-A268-76852380612B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5c85acdc-a394-4ae0-8c72-fb4a95b3d573"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2904,19 +2911,9 @@
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97465A2D-9EAF-44EA-B51B-9ABE6C271840}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{039CDCF7-1F8F-4E25-A268-76852380612B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5c85acdc-a394-4ae0-8c72-fb4a95b3d573"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>